--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/ba-agile-hard.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/ba-agile-hard.xlsx
@@ -460,19 +460,19 @@
         <v>Để tuân thủ tiêu chuẩn INVEST (I - Independent), team có thể sử dụng Mock API/Stubs để kiểm thử logic nghiệp vụ của story mà không bị block bởi các dependencies bên ngoài.</v>
       </c>
       <c r="F2" t="str">
-        <v>Đề xuất team phát triển tạo mock API (dữ liệu giả lập) để tự hoàn thành story độc lập, tránh bị nghẽn tiến độ — giải quyết phụ thuộc</v>
+        <v>Trì hoãn story đó vô thời hạn cho đến khi team kia bàn giao xong API thực tế mới bắt đầu làm — trì hoãn thụ động</v>
       </c>
       <c r="G2" t="str">
-        <v>Trì hoãn story đó vô thời hạn cho đến khi team kia bàn giao xong API thực tế mới bắt đầu làm — trì hoãn thụ động</v>
+        <v>Thay đổi thiết kế để loại bỏ hoàn toàn tính năng gọi API đó ra khỏi hệ thống phần mềm — cắt giảm tính năng</v>
       </c>
       <c r="H2" t="str">
         <v>Yêu cầu lập trình viên của team mình nhảy sang viết hộ code API cho team đối tác — can thiệp nhân sự</v>
       </c>
       <c r="I2" t="str">
-        <v>Thay đổi thiết kế để loại bỏ hoàn toàn tính năng gọi API đó ra khỏi hệ thống phần mềm — cắt giảm tính năng</v>
+        <v>Đề xuất team phát triển tạo mock API (dữ liệu giả lập) để tự hoàn thành story độc lập, tránh bị nghẽn tiến độ — giải quyết phụ thuộc</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         <v>Cắt lát dọc (Vertical Slicing) tạo ra các câu chuyện người dùng hoàn chỉnh từ giao diện đến database. Nhờ đó, người dùng có thể tương tác và phản hồi ngay lập tức, thay vì phải chờ tất cả các tầng kỹ thuật ghép lại.</v>
       </c>
       <c r="F3" t="str">
-        <v>Mỗi story nhỏ đều đi qua đầy đủ các tầng UI-Logic-DB, đảm bảo bàn giao được giá trị chạy thử được cho người dùng — giá trị hoàn chỉnh</v>
+        <v>Giảm thiểu tối đa số lượng test case mà QA cần phải viết cho hệ thống — giảm tải kiểm thử</v>
       </c>
       <c r="G3" t="str">
         <v>Cho phép chia công việc theo kỹ năng chuyên môn: Dev Backend làm riêng, Dev Frontend làm riêng mà không cần nói chuyện — tách biệt công việc</v>
       </c>
       <c r="H3" t="str">
-        <v>Giảm thiểu tối đa số lượng test case mà QA cần phải viết cho hệ thống — giảm tải kiểm thử</v>
+        <v>Mỗi story nhỏ đều đi qua đầy đủ các tầng UI-Logic-DB, đảm bảo bàn giao được giá trị chạy thử được cho người dùng — giá trị hoàn chỉnh</v>
       </c>
       <c r="I3" t="str">
         <v>Giúp tiết kiệm dung lượng lưu trữ cơ sở dữ liệu trên máy chủ Cloud — tối ưu bộ nhớ</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -524,19 +524,19 @@
         <v>Spillage xảy ra liên tục chứng tỏ team chưa nắm vững Velocity thực tế hoặc lập kế hoạch Sprint Planning dựa trên cảm tính, hoặc đưa các yêu cầu chưa sẵn sàng (DoR) vào sprint dẫn đến phát sinh công việc ngoài dự kiến.</v>
       </c>
       <c r="F4" t="str">
-        <v>Team đang ước lượng quá lạc quan, hoặc cam kết vượt quá năng lực thực tế (Velocity), hoặc các story đưa vào sprint chưa đạt DoR — vấn đề lập kế hoạch</v>
+        <v>Khách hàng gửi quá ít yêu cầu thay đổi trong quá trình chạy sprint — thiếu yêu cầu từ khách hàng</v>
       </c>
       <c r="G4" t="str">
         <v>Máy chủ của công ty quá yếu khiến lập trình viên mất nhiều thời gian biên dịch code — vấn đề phần cứng</v>
       </c>
       <c r="H4" t="str">
-        <v>Khách hàng gửi quá ít yêu cầu thay đổi trong quá trình chạy sprint — thiếu yêu cầu từ khách hàng</v>
+        <v>Team đang ước lượng quá lạc quan, hoặc cam kết vượt quá năng lực thực tế (Velocity), hoặc các story đưa vào sprint chưa đạt DoR — vấn đề lập kế hoạch</v>
       </c>
       <c r="I4" t="str">
         <v>Quy trình Definition of Done (DoD) đang quá lỏng lẻo khiến việc nghiệm thu diễn ra quá nhanh — DoD lỏng lẻo</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -556,19 +556,19 @@
         <v>Sự lệch pha giữa User Story và kỳ vọng kinh doanh thường do BA viết câu chuyện quá máy móc hoặc thiếu ngữ cảnh thực tế của người dùng. BA cần cải tiến cách viết Acceptance Criteria (như dùng BDD/Gherkin) để khách hàng dễ hiểu và duyệt trước.</v>
       </c>
       <c r="F5" t="str">
-        <v>Cải tiến hoạt động khơi gợi yêu cầu và xem xét lại cách viết Acceptance Criteria; sử dụng kịch bản nghiệp vụ thực tế thay vì các mô tả kỹ thuật khô khan — tăng chất lượng đặc tả</v>
+        <v>Tăng gấp đôi số lượng Story Point ước lượng cho mỗi tính năng để có thêm thời gian sửa đổi — kéo dài thời gian</v>
       </c>
       <c r="G5" t="str">
         <v>Yêu cầu khách hàng tự viết User Story và chịu trách nhiệm nếu phần mềm chạy không đúng ý — chuyển giao trách nhiệm</v>
       </c>
       <c r="H5" t="str">
-        <v>Tăng gấp đôi số lượng Story Point ước lượng cho mỗi tính năng để có thêm thời gian sửa đổi — kéo dài thời gian</v>
+        <v>Cải tiến hoạt động khơi gợi yêu cầu và xem xét lại cách viết Acceptance Criteria; sử dụng kịch bản nghiệp vụ thực tế thay vì các mô tả kỹ thuật khô khan — tăng chất lượng đặc tả</v>
       </c>
       <c r="I5" t="str">
         <v>Cấm khách hàng tham gia vào buổi họp Sprint Review để tránh nhận ý kiến phản hồi tiêu cực — chặn feedback</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -588,7 +588,7 @@
         <v>Trong các dự án quy mô lớn (như SAFe), PM quản lý định hướng vĩ mô (tầm nhìn, roadmap). PO sở hữu backlog của team. BA đóng vai trò phân tích nghiệp vụ chi tiết, viết User Stories và làm cầu nối kỹ thuật hàng ngày cho team.</v>
       </c>
       <c r="F6" t="str">
-        <v>PM định nghĩa tầm nhìn sản phẩm cấp cao (Features/Roadmap); PO quản lý backlog của Scrum Team; BA hỗ trợ PO đặc tả chi tiết User Story và làm rõ nghiệp vụ cho Dev — phân cấp quản lý yêu cầu</v>
+        <v>PM và PO chỉ làm quản lý nhân sự, toàn bộ việc định hướng sản phẩm do BA chịu trách nhiệm độc lập — BA định hướng</v>
       </c>
       <c r="G6" t="str">
         <v>BA thay thế hoàn toàn vai trò của PO và PM để tự quyết định toàn bộ kiến trúc phần mềm và ký hợp đồng dự án — tập trung quyền lực</v>
@@ -597,10 +597,10 @@
         <v>BA chỉ làm nhiệm vụ vẽ wireframe và thiết kế giao diện đồ họa cho dự án chứ không tham gia viết yêu cầu — thuần UI/UX</v>
       </c>
       <c r="I6" t="str">
-        <v>PM và PO chỉ làm quản lý nhân sự, toàn bộ việc định hướng sản phẩm do BA chịu trách nhiệm độc lập — BA định hướng</v>
+        <v>PM định nghĩa tầm nhìn sản phẩm cấp cao (Features/Roadmap); PO quản lý backlog của Scrum Team; BA hỗ trợ PO đặc tả chi tiết User Story và làm rõ nghiệp vụ cho Dev — phân cấp quản lý yêu cầu</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -620,19 +620,19 @@
         <v>Định dạng Given-When-Then của ngôn ngữ Gherkin giúp cụ thể hóa hành vi hệ thống dưới dạng kịch bản chạy được. Nó giúp thu hẹp khoảng cách hiểu giữa nghiệp vụ (BA/khách hàng) và kỹ thuật (Dev/QA), làm tiền đề cho kiểm thử tự động.</v>
       </c>
       <c r="F7" t="str">
+        <v>Để đảm bảo giao diện người dùng hiển thị đúng các màu sắc và font chữ quy định — ràng buộc giao diện</v>
+      </c>
+      <c r="G7" t="str">
         <v>Để tạo ra một ngôn ngữ chung duy nhất (Ubiquitous Language) mà cả khách hàng, Dev và QA đều hiểu thống nhất, đồng thời có thể tự động hóa thành test scripts — ngôn ngữ chung nhất quán</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Để ép buộc lập trình viên phải sử dụng cấu trúc rẽ nhánh IF-THEN-ELSE khi viết mã nguồn — ràng buộc cấu trúc code</v>
       </c>
       <c r="H7" t="str">
         <v>Để giảm thiểu thời gian BA phải viết tài liệu giải thích nghiệp vụ cho khách hàng — tiết kiệm thời gian BA</v>
       </c>
       <c r="I7" t="str">
-        <v>Để đảm bảo giao diện người dùng hiển thị đúng các màu sắc và font chữ quy định — ràng buộc giao diện</v>
+        <v>Để ép buộc lập trình viên phải sử dụng cấu trúc rẽ nhánh IF-THEN-ELSE khi viết mã nguồn — ràng buộc cấu trúc code</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -684,19 +684,19 @@
         <v>BA là nhà phân tích. Khi có thay đổi giữa chừng, BA phải nhanh chóng làm rõ tác động (về scope, rủi ro, nỗ lực) để cung cấp bức tranh toàn cảnh cho PO đưa ra quyết định sáng suốt và bảo vệ Sprint Goal của team.</v>
       </c>
       <c r="F9" t="str">
+        <v>Tự ý hủy bỏ sprint hiện tại mà không cần sự đồng ý của Scrum Team và PO — lạm quyền quyết định</v>
+      </c>
+      <c r="G9" t="str">
         <v>Hỗ trợ PO thực hiện phân tích tác động (Impact Analysis) của thay đổi, đưa ra các rủi ro về mặt kỹ thuật và tiến độ để PO có cơ sở thương lượng trì hoãn thay đổi sang Sprint sau — điều phối và phân tích tác động</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Lập tức đồng ý với Stakeholders và yêu cầu Dev làm thêm giờ để kịp tiến độ ban đầu mà không cần báo cáo PO — thỏa hiệp thụ động</v>
       </c>
       <c r="H9" t="str">
         <v>Yêu cầu Scrum Master đứng ra kỷ luật PO vì đã vi phạm nguyên tắc Scrum — kỷ luật nội bộ</v>
       </c>
       <c r="I9" t="str">
-        <v>Tự ý hủy bỏ sprint hiện tại mà không cần sự đồng ý của Scrum Team và PO — lạm quyền quyết định</v>
+        <v>Lập tức đồng ý với Stakeholders và yêu cầu Dev làm thêm giờ để kịp tiến độ ban đầu mà không cần báo cáo PO — thỏa hiệp thụ động</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -716,19 +716,19 @@
         <v>Spillover Rate đo lường phần việc bị tràn sang sprint sau. Tỷ lệ này cao chứng tỏ khâu làm mịn yêu cầu (Refinement) chưa tốt, yêu cầu đưa vào sprint còn mơ hồ dẫn đến việc ước lượng sai nỗ lực thực tế.</v>
       </c>
       <c r="F10" t="str">
-        <v>Tỷ lệ phần trăm giữa số Story Points chưa hoàn thành chia cho tổng số Story Points đã cam kết đầu Sprint; phản ánh chất lượng làm mịn yêu cầu (DoR) và ước lượng — đánh giá chất lượng chuẩn bị</v>
+        <v>Tỷ lệ giữa số lượng bug tìm thấy trong sprint chia cho tổng số dòng code; phản ánh chất lượng lập trình của dev — đánh giá chất lượng code</v>
       </c>
       <c r="G10" t="str">
-        <v>Tỷ lệ giữa số lượng bug tìm thấy trong sprint chia cho tổng số dòng code; phản ánh chất lượng lập trình của dev — đánh giá chất lượng code</v>
+        <v>Tỷ lệ giữa số file tài liệu đặc tả bị sửa đổi chia cho tổng số trang tài liệu; phản ánh tính ổn định của tài liệu đặc tả — đánh giá tính ổn định</v>
       </c>
       <c r="H10" t="str">
         <v>Tỷ lệ giữa số buổi họp Daily Scrum bị muộn chia cho tổng số ngày làm việc; phản ánh tính kỷ luật của team — đánh giá tính kỷ luật</v>
       </c>
       <c r="I10" t="str">
-        <v>Tỷ lệ giữa số file tài liệu đặc tả bị sửa đổi chia cho tổng số trang tài liệu; phản ánh tính ổn định của tài liệu đặc tả — đánh giá tính ổn định</v>
+        <v>Tỷ lệ phần trăm giữa số Story Points chưa hoàn thành chia cho tổng số Story Points đã cam kết đầu Sprint; phản ánh chất lượng làm mịn yêu cầu (DoR) và ước lượng — đánh giá chất lượng chuẩn bị</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -748,19 +748,19 @@
         <v>Spike là một tác vụ có khung thời gian cố định (timebox) dùng để nghiên cứu giải pháp kỹ thuật hoặc làm rõ một yêu cầu nghiệp vụ quá mơ hồ, giúp giảm thiểu rủi ro trước khi team cam kết thực hiện story chính thức.</v>
       </c>
       <c r="F11" t="str">
-        <v>Khi gặp một yêu cầu nghiệp vụ hoặc kỹ thuật quá mới mẻ, mơ hồ; cần một khoảng thời gian ngắn để nghiên cứu, thử nghiệm trước khi ước lượng chính thức — nghiên cứu giảm thiểu rủi ro</v>
+        <v>Khi lập trình viên muốn viết code bằng một công nghệ giải trí cá nhân không liên quan đến sản phẩm — nghiên cứu cá nhân</v>
       </c>
       <c r="G11" t="str">
         <v>Khi dự án bị thiếu kinh phí và cần cắt giảm bớt nhân sự phát triển phần mềm — cắt giảm nhân sự</v>
       </c>
       <c r="H11" t="str">
-        <v>Khi lập trình viên muốn viết code bằng một công nghệ giải trí cá nhân không liên quan đến sản phẩm — nghiên cứu cá nhân</v>
+        <v>Khi gặp một yêu cầu nghiệp vụ hoặc kỹ thuật quá mới mẻ, mơ hồ; cần một khoảng thời gian ngắn để nghiên cứu, thử nghiệm trước khi ước lượng chính thức — nghiên cứu giảm thiểu rủi ro</v>
       </c>
       <c r="I11" t="str">
         <v>Khi kiểm thử viên muốn chạy kiểm thử tự động trên môi trường giả lập của đối tác — kiểm thử tự động</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
